--- a/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
+++ b/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="148">
   <si>
     <t>D-Hydro team (BOOT)</t>
   </si>
@@ -437,6 +437,30 @@
   </si>
   <si>
     <t>D-FlowFM: Editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur</t>
+  </si>
+  <si>
+    <t>Do 25 mei: Rehearsal release D-Hydro 1.3.0 / SOBEK 3.7.0</t>
+  </si>
+  <si>
+    <t>Do 22 juni: Release 2017.1 D-Hydro 1.3.1 / SOBEK 3.7.1</t>
+  </si>
+  <si>
+    <t>Patch release NGHS D-Hydro 1.3.2 / SOBEK 3.7.2</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.3 / SOBEK 3.7.3</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.4 / SOBEK 3.7.4</t>
+  </si>
+  <si>
+    <t>Do 12 okt: Rehearsal release D-Hydro 1.3.5 / SOBEK 3.7.5</t>
+  </si>
+  <si>
+    <t>Do 9 nov: Release 2017.2 D-Hydro 1.3.6 / SOBEK 3.7.6</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.7 / SOBEK 3.7.7</t>
   </si>
 </sst>
 </file>
@@ -542,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -639,6 +663,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -646,7 +679,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -764,11 +797,60 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1502,24 +1584,24 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="48">
         <v>42877</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="50">
         <v>0.8</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="7" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="H20" s="38" t="s">
         <v>122</v>
@@ -1532,15 +1614,15 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <v>42884</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="16"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
@@ -1550,19 +1632,17 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="51">
         <v>42891</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="44">
         <v>0.8</v>
       </c>
       <c r="F22" s="16"/>
@@ -1574,15 +1654,17 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="54">
         <v>42898</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="45"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
       <c r="F23" s="18"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
@@ -1596,24 +1678,22 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="57">
         <v>42905</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <v>1</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="10" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>116</v>
@@ -1624,15 +1704,15 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C25" s="51">
         <v>42912</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="16"/>
       <c r="G25" s="3"/>
       <c r="H25" s="38" t="s">
@@ -1642,19 +1722,19 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="54">
         <v>42919</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="55">
         <v>1</v>
       </c>
       <c r="F26" s="16"/>
@@ -1663,19 +1743,19 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="51">
         <v>42926</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="16"/>
       <c r="G27" s="3" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>132</v>
@@ -1686,19 +1766,17 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="51">
         <v>42933</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="44">
         <v>1</v>
       </c>
       <c r="F28" s="16"/>
@@ -1710,15 +1788,17 @@
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="54">
         <v>42940</v>
       </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
       <c r="F29" s="16"/>
       <c r="G29" s="3"/>
       <c r="H29" s="38" t="s">
@@ -1728,19 +1808,17 @@
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="51">
         <v>42947</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="44">
         <v>1</v>
       </c>
       <c r="F30" s="16"/>
@@ -1750,18 +1828,18 @@
       <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41" t="s">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="51">
         <v>42954</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="16"/>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>133</v>
@@ -1772,19 +1850,19 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="54">
         <v>42961</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="55">
         <v>1</v>
       </c>
       <c r="F32" s="16"/>
@@ -1796,15 +1874,15 @@
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="41"/>
-      <c r="B33" s="41" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="42">
+      <c r="C33" s="51">
         <v>42968</v>
       </c>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
       <c r="F33" s="16"/>
       <c r="G33" s="3"/>
       <c r="H33" s="38" t="s">
@@ -1814,19 +1892,17 @@
       <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="51">
         <v>42975</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="44">
         <v>1</v>
       </c>
       <c r="F34" s="16"/>
@@ -1836,20 +1912,22 @@
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41" t="s">
+      <c r="A35" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="54">
         <v>42982</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43" t="s">
+      <c r="D35" s="55"/>
+      <c r="E35" s="55" t="s">
         <v>103</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="3" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1858,19 +1936,17 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="51">
         <v>42989</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="44">
         <v>1</v>
       </c>
       <c r="F36" s="16"/>
@@ -1882,15 +1958,15 @@
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="51">
         <v>42996</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
       <c r="F37" s="16"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
@@ -1900,19 +1976,19 @@
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="54">
         <v>43003</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="55">
         <v>1</v>
       </c>
       <c r="F38" s="16"/>
@@ -1924,15 +2000,15 @@
       <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="42">
+      <c r="C39" s="51">
         <v>43010</v>
       </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
       <c r="F39" s="16"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1942,24 +2018,22 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="59"/>
+      <c r="B40" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="60">
         <v>43017</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="61">
         <v>1</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="7" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H40" s="38" t="s">
         <v>135</v>
@@ -1970,15 +2044,17 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="41"/>
-      <c r="B41" s="41" t="s">
+      <c r="A41" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="42">
+      <c r="C41" s="54">
         <v>43024</v>
       </c>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
       <c r="F41" s="16"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
@@ -1988,19 +2064,17 @@
       <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="51">
         <v>43031</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="44">
         <v>0.8</v>
       </c>
       <c r="F42" s="16"/>
@@ -2014,15 +2088,15 @@
       <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="51">
         <v>43038</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
       <c r="F43" s="16"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -2034,24 +2108,24 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="63">
         <v>43045</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="64">
         <v>1</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="12" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="H44" s="40"/>
       <c r="I44" s="11"/>
@@ -2060,15 +2134,15 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="23"/>
+      <c r="B45" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="51">
         <v>43052</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
       <c r="F45" s="16"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
@@ -2078,19 +2152,17 @@
       <c r="J45" s="3"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="51">
         <v>43059</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="44">
         <v>1</v>
       </c>
       <c r="F46" s="16"/>
@@ -2102,15 +2174,17 @@
       <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="54">
         <v>43066</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
       <c r="F47" s="16"/>
       <c r="G47" s="3"/>
       <c r="H47" s="38" t="s">
@@ -2120,17 +2194,15 @@
       <c r="J47" s="3"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="A48" s="23"/>
+      <c r="B48" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="51">
         <v>43073</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16">
+      <c r="D48" s="44"/>
+      <c r="E48" s="44">
         <v>1</v>
       </c>
       <c r="F48" s="16"/>
@@ -2142,18 +2214,18 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="23"/>
+      <c r="B49" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="51">
         <v>43080</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
       <c r="F49" s="16"/>
       <c r="G49" s="3" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -2189,7 +2261,7 @@
       </c>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
-      <c r="D52" s="46" t="s">
+      <c r="D52" s="45" t="s">
         <v>83</v>
       </c>
       <c r="E52" s="28"/>
@@ -2203,7 +2275,7 @@
       <c r="A53" s="30"/>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E53" s="24"/>
@@ -2217,7 +2289,7 @@
       <c r="A54" s="30"/>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="46" t="s">
         <v>84</v>
       </c>
       <c r="E54" s="23"/>
@@ -2231,7 +2303,7 @@
       <c r="A55" s="30"/>
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
-      <c r="D55" s="47" t="s">
+      <c r="D55" s="46" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="23"/>

--- a/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
+++ b/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
@@ -679,7 +679,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -851,6 +851,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2108,8 +2111,8 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="62" t="s">
-        <v>60</v>
+      <c r="A44" s="65" t="s">
+        <v>49</v>
       </c>
       <c r="B44" s="62" t="s">
         <v>62</v>
@@ -2175,7 +2178,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="53" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B47" s="53" t="s">
         <v>66</v>
@@ -3040,7 +3043,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -3059,7 +3062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -3078,7 +3081,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>45</v>
@@ -3093,7 +3096,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -3112,7 +3115,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>48</v>
@@ -3133,7 +3136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
@@ -3154,7 +3157,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>52</v>
@@ -3171,7 +3174,7 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>51</v>
       </c>
@@ -3192,7 +3195,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>55</v>

--- a/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
+++ b/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="148">
   <si>
     <t>D-Hydro team (BOOT)</t>
   </si>
@@ -437,6 +437,30 @@
   </si>
   <si>
     <t>D-FlowFM: Editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur</t>
+  </si>
+  <si>
+    <t>Do 25 mei: Rehearsal release D-Hydro 1.3.0 / SOBEK 3.7.0</t>
+  </si>
+  <si>
+    <t>Do 22 juni: Release 2017.1 D-Hydro 1.3.1 / SOBEK 3.7.1</t>
+  </si>
+  <si>
+    <t>Patch release NGHS D-Hydro 1.3.2 / SOBEK 3.7.2</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.3 / SOBEK 3.7.3</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.4 / SOBEK 3.7.4</t>
+  </si>
+  <si>
+    <t>Do 12 okt: Rehearsal release D-Hydro 1.3.5 / SOBEK 3.7.5</t>
+  </si>
+  <si>
+    <t>Do 9 nov: Release 2017.2 D-Hydro 1.3.6 / SOBEK 3.7.6</t>
+  </si>
+  <si>
+    <t>Patch release D-Hydro 1.3.7 / SOBEK 3.7.7</t>
   </si>
 </sst>
 </file>
@@ -542,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -639,6 +663,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -646,7 +679,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -764,11 +797,63 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="4" borderId="10" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1502,24 +1587,24 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="48">
         <v>42877</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="50">
         <v>0.8</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="7" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="H20" s="38" t="s">
         <v>122</v>
@@ -1532,15 +1617,15 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="42">
+      <c r="C21" s="51">
         <v>42884</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
       <c r="F21" s="16"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
@@ -1550,19 +1635,17 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="51">
         <v>42891</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="44">
         <v>0.8</v>
       </c>
       <c r="F22" s="16"/>
@@ -1574,15 +1657,17 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41" t="s">
+      <c r="A23" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="54">
         <v>42898</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="45"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="56"/>
       <c r="F23" s="18"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
@@ -1596,24 +1681,22 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="57">
         <v>42905</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <v>1</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="10" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>116</v>
@@ -1624,15 +1707,15 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C25" s="51">
         <v>42912</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="16"/>
       <c r="G25" s="3"/>
       <c r="H25" s="38" t="s">
@@ -1642,19 +1725,19 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="54">
         <v>42919</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="55">
         <v>1</v>
       </c>
       <c r="F26" s="16"/>
@@ -1663,19 +1746,19 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="51">
         <v>42926</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="16"/>
       <c r="G27" s="3" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>132</v>
@@ -1686,19 +1769,17 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="51">
         <v>42933</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="44">
         <v>1</v>
       </c>
       <c r="F28" s="16"/>
@@ -1710,15 +1791,17 @@
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41" t="s">
+      <c r="A29" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="54">
         <v>42940</v>
       </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
       <c r="F29" s="16"/>
       <c r="G29" s="3"/>
       <c r="H29" s="38" t="s">
@@ -1728,19 +1811,17 @@
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="51">
         <v>42947</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="44">
         <v>1</v>
       </c>
       <c r="F30" s="16"/>
@@ -1750,18 +1831,18 @@
       <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41" t="s">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="42">
+      <c r="C31" s="51">
         <v>42954</v>
       </c>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="16"/>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>133</v>
@@ -1772,19 +1853,19 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="54">
         <v>42961</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="55">
         <v>1</v>
       </c>
       <c r="F32" s="16"/>
@@ -1796,15 +1877,15 @@
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="41"/>
-      <c r="B33" s="41" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="42">
+      <c r="C33" s="51">
         <v>42968</v>
       </c>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
       <c r="F33" s="16"/>
       <c r="G33" s="3"/>
       <c r="H33" s="38" t="s">
@@ -1814,19 +1895,17 @@
       <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="51">
         <v>42975</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="44">
         <v>1</v>
       </c>
       <c r="F34" s="16"/>
@@ -1836,20 +1915,22 @@
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="41" t="s">
+      <c r="A35" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="54">
         <v>42982</v>
       </c>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43" t="s">
+      <c r="D35" s="55"/>
+      <c r="E35" s="55" t="s">
         <v>103</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="3" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1858,19 +1939,17 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="51">
         <v>42989</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="44">
         <v>1</v>
       </c>
       <c r="F36" s="16"/>
@@ -1882,15 +1961,15 @@
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="42">
+      <c r="C37" s="51">
         <v>42996</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
       <c r="F37" s="16"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
@@ -1900,19 +1979,19 @@
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="54">
         <v>43003</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="55">
         <v>1</v>
       </c>
       <c r="F38" s="16"/>
@@ -1924,15 +2003,15 @@
       <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="42">
+      <c r="C39" s="51">
         <v>43010</v>
       </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
       <c r="F39" s="16"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
@@ -1942,24 +2021,22 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="59"/>
+      <c r="B40" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="60">
         <v>43017</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="61">
         <v>1</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="7" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="H40" s="38" t="s">
         <v>135</v>
@@ -1970,15 +2047,17 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="41"/>
-      <c r="B41" s="41" t="s">
+      <c r="A41" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="42">
+      <c r="C41" s="54">
         <v>43024</v>
       </c>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
       <c r="F41" s="16"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
@@ -1988,19 +2067,17 @@
       <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="51">
         <v>43031</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="44">
         <v>0.8</v>
       </c>
       <c r="F42" s="16"/>
@@ -2014,15 +2091,15 @@
       <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="51">
         <v>43038</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
       <c r="F43" s="16"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -2034,24 +2111,24 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" s="8" t="s">
+      <c r="A44" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="63">
         <v>43045</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E44" s="64">
         <v>1</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="12" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="H44" s="40"/>
       <c r="I44" s="11"/>
@@ -2060,15 +2137,15 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="23"/>
+      <c r="B45" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="51">
         <v>43052</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
       <c r="F45" s="16"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
@@ -2078,19 +2155,17 @@
       <c r="J45" s="3"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="51">
         <v>43059</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="44">
         <v>1</v>
       </c>
       <c r="F46" s="16"/>
@@ -2102,15 +2177,17 @@
       <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="54">
         <v>43066</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
       <c r="F47" s="16"/>
       <c r="G47" s="3"/>
       <c r="H47" s="38" t="s">
@@ -2120,17 +2197,15 @@
       <c r="J47" s="3"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="A48" s="23"/>
+      <c r="B48" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="51">
         <v>43073</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16">
+      <c r="D48" s="44"/>
+      <c r="E48" s="44">
         <v>1</v>
       </c>
       <c r="F48" s="16"/>
@@ -2142,18 +2217,18 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="23"/>
+      <c r="B49" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="51">
         <v>43080</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
       <c r="F49" s="16"/>
       <c r="G49" s="3" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -2189,7 +2264,7 @@
       </c>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
-      <c r="D52" s="46" t="s">
+      <c r="D52" s="45" t="s">
         <v>83</v>
       </c>
       <c r="E52" s="28"/>
@@ -2203,7 +2278,7 @@
       <c r="A53" s="30"/>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="46" t="s">
         <v>129</v>
       </c>
       <c r="E53" s="24"/>
@@ -2217,7 +2292,7 @@
       <c r="A54" s="30"/>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="46" t="s">
         <v>84</v>
       </c>
       <c r="E54" s="23"/>
@@ -2231,7 +2306,7 @@
       <c r="A55" s="30"/>
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
-      <c r="D55" s="47" t="s">
+      <c r="D55" s="46" t="s">
         <v>102</v>
       </c>
       <c r="E55" s="23"/>
@@ -2968,7 +3043,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -2987,7 +3062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -3006,7 +3081,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>45</v>
@@ -3021,7 +3096,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -3040,7 +3115,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>48</v>
@@ -3061,7 +3136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
@@ -3082,7 +3157,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>52</v>
@@ -3099,7 +3174,7 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>51</v>
       </c>
@@ -3120,7 +3195,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>55</v>

--- a/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
+++ b/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="149">
   <si>
     <t>D-Hydro team (BOOT)</t>
   </si>
@@ -331,9 +331,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>D-RR and D-NAM</t>
-  </si>
-  <si>
     <t>teamfocus</t>
   </si>
   <si>
@@ -433,12 +430,6 @@
     <t>Planning 31 march</t>
   </si>
   <si>
-    <t xml:space="preserve">D-FlowFM: Editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur </t>
-  </si>
-  <si>
-    <t>D-FlowFM: Editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur</t>
-  </si>
-  <si>
     <t>Do 25 mei: Rehearsal release D-Hydro 1.3.0 / SOBEK 3.7.0</t>
   </si>
   <si>
@@ -461,6 +452,18 @@
   </si>
   <si>
     <t>Patch release D-Hydro 1.3.7 / SOBEK 3.7.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-FlowFM: 6e generation-&gt; editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur </t>
+  </si>
+  <si>
+    <t>D-FlowFM: 6e generation-&gt; editor voor General structure (M), Visualisatie Grid snapped features (S), Observationpoints en mappenstructuur</t>
+  </si>
+  <si>
+    <t>2D Flooding Extra  Polder, Release bugs</t>
+  </si>
+  <si>
+    <t>2D Flooding Extra  Polder, Release bugs, GUI edit links breach grow scripts</t>
   </si>
 </sst>
 </file>
@@ -818,7 +821,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -856,6 +858,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
@@ -1183,7 +1186,7 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
@@ -1203,7 +1206,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1222,16 +1225,16 @@
         <v>99</v>
       </c>
       <c r="E3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>70</v>
@@ -1257,7 +1260,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -1275,7 +1278,7 @@
       <c r="D5" s="43"/>
       <c r="E5" s="43"/>
       <c r="F5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1299,7 +1302,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1317,7 +1320,7 @@
       <c r="D7" s="43"/>
       <c r="E7" s="43"/>
       <c r="F7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>88</v>
@@ -1345,7 +1348,7 @@
         <v>0.7</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -1363,7 +1366,7 @@
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
       <c r="F9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -1381,13 +1384,13 @@
         <v>42807</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E10" s="16">
         <v>0.7</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1409,7 +1412,7 @@
         <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
@@ -1427,7 +1430,7 @@
         <v>42821</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" s="16">
         <v>0.7</v>
@@ -1435,7 +1438,7 @@
       <c r="F12" s="16"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1453,7 +1456,7 @@
       <c r="F13" s="16"/>
       <c r="G13" s="3"/>
       <c r="H13" s="38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>71</v>
@@ -1471,7 +1474,7 @@
         <v>42835</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E14" s="16">
         <v>0.7</v>
@@ -1513,7 +1516,7 @@
         <v>42849</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" s="16">
         <v>0.6</v>
@@ -1521,7 +1524,7 @@
       <c r="F16" s="16"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -1539,7 +1542,7 @@
       <c r="F17" s="44"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1555,7 +1558,7 @@
         <v>42863</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E18" s="16">
         <v>0.6</v>
@@ -1563,7 +1566,7 @@
       <c r="F18" s="16"/>
       <c r="G18" s="3"/>
       <c r="H18" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -1597,20 +1600,20 @@
         <v>42877</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" s="50">
         <v>0.8</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>78</v>
@@ -1629,7 +1632,7 @@
       <c r="F21" s="16"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1642,8 +1645,8 @@
       <c r="C22" s="51">
         <v>42891</v>
       </c>
-      <c r="D22" s="52" t="s">
-        <v>128</v>
+      <c r="D22" s="65" t="s">
+        <v>147</v>
       </c>
       <c r="E22" s="44">
         <v>0.8</v>
@@ -1651,27 +1654,27 @@
       <c r="F22" s="16"/>
       <c r="G22" s="3"/>
       <c r="H22" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="53">
         <v>42898</v>
       </c>
-      <c r="D23" s="55"/>
-      <c r="E23" s="56"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="18"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>73</v>
@@ -1680,26 +1683,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="56">
         <v>42905</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>138</v>
+      <c r="D24" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="E24" s="20">
         <v>1</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="10" t="s">
@@ -1719,25 +1722,25 @@
       <c r="F25" s="16"/>
       <c r="G25" s="3"/>
       <c r="H25" s="38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="53">
         <v>42919</v>
       </c>
-      <c r="D26" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="55">
+      <c r="D26" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="54">
         <v>1</v>
       </c>
       <c r="F26" s="16"/>
@@ -1758,17 +1761,17 @@
       <c r="E27" s="44"/>
       <c r="F27" s="16"/>
       <c r="G27" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="23"/>
       <c r="B28" s="23" t="s">
         <v>38</v>
@@ -1777,7 +1780,7 @@
         <v>42933</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="E28" s="44">
         <v>1</v>
@@ -1785,27 +1788,27 @@
       <c r="F28" s="16"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="53">
         <v>42940</v>
       </c>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
       <c r="F29" s="16"/>
       <c r="G29" s="3"/>
       <c r="H29" s="38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -1818,7 +1821,7 @@
       <c r="C30" s="51">
         <v>42947</v>
       </c>
-      <c r="D30" s="58" t="s">
+      <c r="D30" s="57" t="s">
         <v>81</v>
       </c>
       <c r="E30" s="44">
@@ -1842,10 +1845,10 @@
       <c r="E31" s="44"/>
       <c r="F31" s="16"/>
       <c r="G31" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
@@ -1853,25 +1856,25 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="53" t="s">
+      <c r="A32" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="54">
+      <c r="C32" s="53">
         <v>42961</v>
       </c>
-      <c r="D32" s="55" t="s">
+      <c r="D32" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="54">
         <v>1</v>
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -1889,7 +1892,7 @@
       <c r="F33" s="16"/>
       <c r="G33" s="3"/>
       <c r="H33" s="38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -1903,7 +1906,7 @@
         <v>42975</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="44">
         <v>1</v>
@@ -1915,22 +1918,22 @@
       <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="54">
+      <c r="C35" s="53">
         <v>42982</v>
       </c>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55" t="s">
+      <c r="D35" s="54"/>
+      <c r="E35" s="54" t="s">
         <v>103</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1955,7 +1958,7 @@
       <c r="F36" s="16"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -1973,31 +1976,31 @@
       <c r="F37" s="16"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="C38" s="54">
+      <c r="C38" s="53">
         <v>43003</v>
       </c>
-      <c r="D38" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="55">
+      <c r="D38" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="54">
         <v>1</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="3"/>
       <c r="H38" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -2021,25 +2024,25 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
-      <c r="B40" s="59" t="s">
+      <c r="A40" s="58"/>
+      <c r="B40" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="60">
+      <c r="C40" s="59">
         <v>43017</v>
       </c>
-      <c r="D40" s="59" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="61">
+      <c r="D40" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" s="60">
         <v>1</v>
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="7" t="s">
@@ -2047,21 +2050,21 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="54">
+      <c r="C41" s="53">
         <v>43024</v>
       </c>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
       <c r="F41" s="16"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -2074,7 +2077,7 @@
       <c r="C42" s="51">
         <v>43031</v>
       </c>
-      <c r="D42" s="58" t="s">
+      <c r="D42" s="57" t="s">
         <v>86</v>
       </c>
       <c r="E42" s="44">
@@ -2083,7 +2086,7 @@
       <c r="F42" s="16"/>
       <c r="G42" s="3"/>
       <c r="H42" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>72</v>
@@ -2111,24 +2114,24 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="63">
+      <c r="C44" s="62">
         <v>43045</v>
       </c>
-      <c r="D44" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" s="64">
+      <c r="D44" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="63">
         <v>1</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H44" s="40"/>
       <c r="I44" s="11"/>
@@ -2149,7 +2152,7 @@
       <c r="F45" s="16"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
@@ -2171,27 +2174,27 @@
       <c r="F46" s="16"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="53" t="s">
+      <c r="B47" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="54">
+      <c r="C47" s="53">
         <v>43066</v>
       </c>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
       <c r="F47" s="16"/>
       <c r="G47" s="3"/>
       <c r="H47" s="38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -2228,7 +2231,7 @@
       <c r="E49" s="44"/>
       <c r="F49" s="16"/>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -2279,7 +2282,7 @@
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
       <c r="D53" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
@@ -2496,7 +2499,7 @@
       <c r="E2" s="13"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -2512,16 +2515,16 @@
         <v>74</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>70</v>
@@ -2541,7 +2544,7 @@
         <v>42765</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4" s="16">
         <v>0.5</v>
@@ -2559,7 +2562,7 @@
         <v>42772</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="3"/>
@@ -2577,7 +2580,7 @@
         <v>42779</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" s="16">
         <v>0.5</v>
@@ -2595,7 +2598,7 @@
         <v>42786</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="3" t="s">
@@ -2617,7 +2620,7 @@
         <v>42793</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="16">
         <v>0.7</v>
@@ -2635,7 +2638,7 @@
         <v>42800</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="3"/>
@@ -2653,7 +2656,7 @@
         <v>42807</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" s="16">
         <v>0.7</v>
@@ -2676,7 +2679,7 @@
         <v>89</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
@@ -2772,7 +2775,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -2789,7 +2792,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -2810,7 +2813,7 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -2850,7 +2853,7 @@
         <v>91</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="7" t="s">
@@ -2869,7 +2872,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -2890,7 +2893,7 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -3152,7 +3155,7 @@
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -3169,7 +3172,7 @@
       <c r="E37" s="16"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -3190,7 +3193,7 @@
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -3230,7 +3233,7 @@
         <v>95</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="7" t="s">
@@ -3249,7 +3252,7 @@
       <c r="E41" s="16"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -3270,7 +3273,7 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>72</v>

--- a/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
+++ b/documents/planning/BOOT-SprintGoals  Releases 2017.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="120" windowWidth="16605" windowHeight="9435"/>
+    <workbookView xWindow="360" yWindow="120" windowWidth="16608" windowHeight="9432"/>
   </bookViews>
   <sheets>
     <sheet name="D-Shell en kernels" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
   <si>
     <t>D-Hydro team (BOOT)</t>
   </si>
@@ -409,24 +409,6 @@
     <t>Feature freeze kernels 1.2.7</t>
   </si>
   <si>
-    <t>Feature freeze kernels 1.2.10</t>
-  </si>
-  <si>
-    <t>Feature freeze kernels 1.2.11</t>
-  </si>
-  <si>
-    <t>Feature freeze kernels 1.2.12</t>
-  </si>
-  <si>
-    <t>Feature freeze kernels 1.2.13</t>
-  </si>
-  <si>
-    <t>Feature freeze kernels 1.2.14</t>
-  </si>
-  <si>
-    <t>Feature freeze kernels 1.2.15</t>
-  </si>
-  <si>
     <t>Planning 31 march</t>
   </si>
   <si>
@@ -464,6 +446,24 @@
   </si>
   <si>
     <t>2D Flooding Extra  Polder, Release bugs, GUI edit links breach grow scripts</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.2</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.3</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.4</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.5</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.6</t>
+  </si>
+  <si>
+    <t>Delivery to Delta Shell 1.3.7</t>
   </si>
 </sst>
 </file>
@@ -1164,19 +1164,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="56.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="56.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="31.7109375" customWidth="1"/>
-    <col min="7" max="7" width="45.28515625" customWidth="1"/>
-    <col min="8" max="8" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.42578125" customWidth="1"/>
-    <col min="10" max="10" width="28.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="7" max="7" width="45.33203125" customWidth="1"/>
+    <col min="8" max="8" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" customWidth="1"/>
+    <col min="10" max="10" width="28.6640625" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
@@ -1186,7 +1186,7 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
@@ -1267,7 +1267,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="41"/>
       <c r="B5" s="41" t="s">
         <v>3</v>
@@ -1285,7 +1285,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1309,7 +1309,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="41"/>
       <c r="B7" s="41" t="s">
         <v>6</v>
@@ -1355,7 +1355,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="41" t="s">
         <v>9</v>
@@ -1373,7 +1373,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="28.95" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1397,7 +1397,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="41"/>
       <c r="B11" s="41" t="s">
         <v>12</v>
@@ -1419,7 +1419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -1443,7 +1443,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="41"/>
       <c r="B13" s="41" t="s">
         <v>15</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1485,7 +1485,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="41"/>
       <c r="B15" s="41" t="s">
         <v>18</v>
@@ -1505,7 +1505,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="41"/>
       <c r="B17" s="41" t="s">
         <v>21</v>
@@ -1547,7 +1547,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="41"/>
       <c r="B19" s="41" t="s">
         <v>24</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H20" s="38" t="s">
         <v>121</v>
@@ -1619,7 +1619,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="B21" s="23" t="s">
         <v>27</v>
@@ -1637,7 +1637,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="23"/>
       <c r="B22" s="23" t="s">
         <v>29</v>
@@ -1646,7 +1646,7 @@
         <v>42891</v>
       </c>
       <c r="D22" s="65" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E22" s="44">
         <v>0.8</v>
@@ -1659,7 +1659,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="52" t="s">
         <v>28</v>
       </c>
@@ -1673,9 +1673,7 @@
       <c r="E23" s="55"/>
       <c r="F23" s="18"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
         <v>73</v>
       </c>
@@ -1683,7 +1681,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="11" t="s">
         <v>32</v>
@@ -1692,24 +1690,22 @@
         <v>42905</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E24" s="20">
         <v>1</v>
       </c>
       <c r="F24" s="19"/>
       <c r="G24" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>115</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="H24" s="3"/>
       <c r="I24" s="8"/>
       <c r="J24" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
       <c r="B25" s="23" t="s">
         <v>33</v>
@@ -1722,7 +1718,7 @@
       <c r="F25" s="16"/>
       <c r="G25" s="3"/>
       <c r="H25" s="38" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -1738,7 +1734,7 @@
         <v>42919</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E26" s="54">
         <v>1</v>
@@ -1749,7 +1745,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
       <c r="B27" s="23" t="s">
         <v>36</v>
@@ -1761,17 +1757,15 @@
       <c r="E27" s="44"/>
       <c r="F27" s="16"/>
       <c r="G27" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>131</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
       <c r="B28" s="23" t="s">
         <v>38</v>
@@ -1780,20 +1774,18 @@
         <v>42933</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E28" s="44">
         <v>1</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="52" t="s">
         <v>34</v>
       </c>
@@ -1808,12 +1800,12 @@
       <c r="F29" s="16"/>
       <c r="G29" s="3"/>
       <c r="H29" s="38" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="23"/>
       <c r="B30" s="23" t="s">
         <v>41</v>
@@ -1833,7 +1825,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
       <c r="B31" s="23" t="s">
         <v>42</v>
@@ -1845,17 +1837,15 @@
       <c r="E31" s="44"/>
       <c r="F31" s="16"/>
       <c r="G31" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="52" t="s">
         <v>37</v>
       </c>
@@ -1873,13 +1863,11 @@
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
       <c r="B33" s="23" t="s">
         <v>45</v>
@@ -1892,12 +1880,12 @@
       <c r="F33" s="16"/>
       <c r="G33" s="3"/>
       <c r="H33" s="38" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
       <c r="B34" s="23" t="s">
         <v>47</v>
@@ -1917,7 +1905,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="52" t="s">
         <v>40</v>
       </c>
@@ -1933,7 +1921,7 @@
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1941,7 +1929,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="23"/>
       <c r="B36" s="23" t="s">
         <v>50</v>
@@ -1957,13 +1945,11 @@
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="23"/>
       <c r="B37" s="23" t="s">
         <v>52</v>
@@ -1975,13 +1961,11 @@
       <c r="E37" s="44"/>
       <c r="F37" s="16"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="52" t="s">
         <v>43</v>
       </c>
@@ -2000,12 +1984,12 @@
       <c r="F38" s="16"/>
       <c r="G38" s="3"/>
       <c r="H38" s="7" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
       <c r="B39" s="23" t="s">
         <v>55</v>
@@ -2023,7 +2007,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="58"/>
       <c r="B40" s="58" t="s">
         <v>56</v>
@@ -2039,17 +2023,15 @@
       </c>
       <c r="F40" s="17"/>
       <c r="G40" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H40" s="38" t="s">
-        <v>134</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="H40" s="38"/>
       <c r="I40" s="5"/>
       <c r="J40" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="52" t="s">
         <v>46</v>
       </c>
@@ -2063,13 +2045,11 @@
       <c r="E41" s="54"/>
       <c r="F41" s="16"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="23"/>
       <c r="B42" s="23" t="s">
         <v>59</v>
@@ -2086,14 +2066,14 @@
       <c r="F42" s="16"/>
       <c r="G42" s="3"/>
       <c r="H42" s="12" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>72</v>
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
       <c r="B43" s="23" t="s">
         <v>61</v>
@@ -2131,7 +2111,7 @@
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="H44" s="40"/>
       <c r="I44" s="11"/>
@@ -2139,7 +2119,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="23"/>
       <c r="B45" s="23" t="s">
         <v>64</v>
@@ -2151,13 +2131,11 @@
       <c r="E45" s="44"/>
       <c r="F45" s="16"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3" t="s">
-        <v>135</v>
-      </c>
+      <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="23"/>
       <c r="B46" s="23" t="s">
         <v>65</v>
@@ -2173,13 +2151,11 @@
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="52" t="s">
         <v>51</v>
       </c>
@@ -2194,12 +2170,12 @@
       <c r="F47" s="16"/>
       <c r="G47" s="3"/>
       <c r="H47" s="38" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
       <c r="B48" s="23" t="s">
         <v>67</v>
@@ -2219,7 +2195,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="23"/>
       <c r="B49" s="23" t="s">
         <v>68</v>
@@ -2231,13 +2207,13 @@
       <c r="E49" s="44"/>
       <c r="F49" s="16"/>
       <c r="G49" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
@@ -2277,7 +2253,7 @@
       <c r="I52" s="27"/>
       <c r="J52" s="29"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="30"/>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
@@ -2291,7 +2267,7 @@
       <c r="I53" s="23"/>
       <c r="J53" s="31"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="30"/>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
@@ -2305,7 +2281,7 @@
       <c r="I54" s="23"/>
       <c r="J54" s="31"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="30"/>
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
@@ -2319,7 +2295,7 @@
       <c r="I55" s="23"/>
       <c r="J55" s="31"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="30"/>
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
@@ -2331,7 +2307,7 @@
       <c r="I56" s="23"/>
       <c r="J56" s="31"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="32"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -2343,7 +2319,7 @@
       <c r="I57" s="25"/>
       <c r="J57" s="33"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="32"/>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -2355,7 +2331,7 @@
       <c r="I58" s="25"/>
       <c r="J58" s="33"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="32"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -2367,7 +2343,7 @@
       <c r="I59" s="25"/>
       <c r="J59" s="33"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="32"/>
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
@@ -2379,7 +2355,7 @@
       <c r="I60" s="25"/>
       <c r="J60" s="33"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="32"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -2391,7 +2367,7 @@
       <c r="I61" s="25"/>
       <c r="J61" s="33"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="32"/>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
@@ -2403,7 +2379,7 @@
       <c r="I62" s="25"/>
       <c r="J62" s="33"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="32"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -2415,7 +2391,7 @@
       <c r="I63" s="25"/>
       <c r="J63" s="33"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="32"/>
       <c r="B64" s="25"/>
       <c r="C64" s="25"/>
@@ -2427,7 +2403,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="33"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="32"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -2439,7 +2415,7 @@
       <c r="I65" s="25"/>
       <c r="J65" s="33"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="34"/>
       <c r="B66" s="35"/>
       <c r="C66" s="35"/>
@@ -2460,18 +2436,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="56.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="56.33203125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="45.28515625" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="45.33203125" customWidth="1"/>
+    <col min="7" max="7" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.44140625" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
@@ -2533,7 +2509,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2553,7 +2529,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>3</v>
@@ -2569,7 +2545,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -2589,7 +2565,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -2609,7 +2585,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2629,7 +2605,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -2645,7 +2621,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -2665,7 +2641,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
@@ -2686,7 +2662,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -2705,7 +2681,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>15</v>
@@ -2722,7 +2698,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
@@ -2740,7 +2716,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>18</v>
@@ -2759,7 +2735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
@@ -2780,7 +2756,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>21</v>
@@ -2797,7 +2773,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -2818,7 +2794,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>24</v>
@@ -2860,7 +2836,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>27</v>
@@ -2877,7 +2853,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
@@ -2898,7 +2874,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>30</v>
@@ -2940,7 +2916,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>33</v>
@@ -2955,7 +2931,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
@@ -2993,7 +2969,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
@@ -3012,7 +2988,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3027,7 +3003,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
@@ -3046,7 +3022,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -3065,7 +3041,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>43</v>
       </c>
@@ -3084,7 +3060,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>45</v>
@@ -3099,7 +3075,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>46</v>
       </c>
@@ -3118,7 +3094,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>48</v>
@@ -3139,7 +3115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
@@ -3160,7 +3136,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>52</v>
@@ -3177,7 +3153,7 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>51</v>
       </c>
@@ -3198,7 +3174,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>55</v>
@@ -3215,7 +3191,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>54</v>
       </c>
@@ -3240,7 +3216,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>58</v>
@@ -3257,7 +3233,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>57</v>
       </c>
@@ -3280,7 +3256,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>61</v>
@@ -3299,7 +3275,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>60</v>
       </c>
@@ -3322,7 +3298,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>64</v>
@@ -3337,7 +3313,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>63</v>
       </c>
@@ -3356,7 +3332,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>66</v>
@@ -3371,7 +3347,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>69</v>
       </c>
@@ -3392,7 +3368,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>68</v>
@@ -3409,7 +3385,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
@@ -3420,7 +3396,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3431,7 +3407,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="26" t="s">
         <v>79</v>
       </c>
@@ -3444,7 +3420,7 @@
       <c r="H52" s="27"/>
       <c r="I52" s="29"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="30"/>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
@@ -3457,7 +3433,7 @@
       <c r="H53" s="23"/>
       <c r="I53" s="31"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="30"/>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
@@ -3470,7 +3446,7 @@
       <c r="H54" s="23"/>
       <c r="I54" s="31"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="30"/>
       <c r="B55" s="23"/>
       <c r="C55" s="23"/>
@@ -3483,7 +3459,7 @@
       <c r="H55" s="23"/>
       <c r="I55" s="31"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="30"/>
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
@@ -3494,7 +3470,7 @@
       <c r="H56" s="23"/>
       <c r="I56" s="31"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="32"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -3505,7 +3481,7 @@
       <c r="H57" s="25"/>
       <c r="I57" s="33"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="32"/>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -3516,7 +3492,7 @@
       <c r="H58" s="25"/>
       <c r="I58" s="33"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="32"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -3527,7 +3503,7 @@
       <c r="H59" s="25"/>
       <c r="I59" s="33"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="32"/>
       <c r="B60" s="25"/>
       <c r="C60" s="25"/>
@@ -3538,7 +3514,7 @@
       <c r="H60" s="25"/>
       <c r="I60" s="33"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="32"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -3549,7 +3525,7 @@
       <c r="H61" s="25"/>
       <c r="I61" s="33"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="32"/>
       <c r="B62" s="25"/>
       <c r="C62" s="25"/>
@@ -3560,7 +3536,7 @@
       <c r="H62" s="25"/>
       <c r="I62" s="33"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="32"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -3571,7 +3547,7 @@
       <c r="H63" s="25"/>
       <c r="I63" s="33"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="32"/>
       <c r="B64" s="25"/>
       <c r="C64" s="25"/>
@@ -3582,7 +3558,7 @@
       <c r="H64" s="25"/>
       <c r="I64" s="33"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="32"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -3593,7 +3569,7 @@
       <c r="H65" s="25"/>
       <c r="I65" s="33"/>
     </row>
-    <row r="66" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="34"/>
       <c r="B66" s="35"/>
       <c r="C66" s="35"/>
@@ -3613,7 +3589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3622,7 +3598,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
